--- a/TestData/Coursera_latest.xlsx
+++ b/TestData/Coursera_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2464428\IdeaProjects\Identify_Courses_Coursera\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B11968-81DA-4943-BE79-4D3EE98AF2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176E957D-C058-4B19-BE29-8C74BC330DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>FirstName</t>
   </si>
@@ -554,8 +554,8 @@
       <c r="D2">
         <v>1234567890</v>
       </c>
-      <c r="E2" t="s">
-        <v>15</v>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
